--- a/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 9,69</t>
+          <t>-7,54; 9,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 10,54</t>
+          <t>-5,49; 9,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 10,38</t>
+          <t>-6,52; 9,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 33,77</t>
+          <t>-4,84; 34,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 50,09</t>
+          <t>-28,45; 54,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 61,89</t>
+          <t>-23,56; 64,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 83,85</t>
+          <t>-31,5; 80,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 914,11</t>
+          <t>-51,88; 991,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 4,62</t>
+          <t>-9,15; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 8,36</t>
+          <t>-3,53; 8,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,18</t>
+          <t>-5,14; 6,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 11,06</t>
+          <t>-20,74; 11,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 27,6</t>
+          <t>-38,2; 24,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 69,23</t>
+          <t>-20,73; 73,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 50,98</t>
+          <t>-25,85; 46,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,41; 63,44</t>
+          <t>-66,29; 63,4</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 14,04</t>
+          <t>-1,55; 13,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 5,83</t>
+          <t>-8,53; 6,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 1,96</t>
+          <t>-13,78; 2,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 24,64</t>
+          <t>-11,47; 24,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 92,16</t>
+          <t>-6,25; 97,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 38,06</t>
+          <t>-36,59; 40,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 9,91</t>
+          <t>-48,12; 10,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 323,49</t>
+          <t>-58,13; 320,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 14,12</t>
+          <t>-0,41; 14,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 10,8</t>
+          <t>-3,38; 10,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 7,15</t>
+          <t>-7,17; 6,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 12,24</t>
+          <t>-21,49; 10,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 91,06</t>
+          <t>-1,1; 90,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 61,17</t>
+          <t>-13,53; 60,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 43,93</t>
+          <t>-30,84; 42,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 125,45</t>
+          <t>-78,22; 115,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 6,81</t>
+          <t>-0,7; 6,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,5</t>
+          <t>-1,39; 6,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,25</t>
+          <t>-3,93; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 10,24</t>
+          <t>-8,02; 8,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 38,51</t>
+          <t>-3,08; 37,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 32,42</t>
+          <t>-6,93; 35,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 19,2</t>
+          <t>-18,51; 15,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 69,03</t>
+          <t>-35,03; 56,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 9,88</t>
+          <t>-6,24; 11,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 9,98</t>
+          <t>-5,94; 10,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 9,68</t>
+          <t>-7,02; 9,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 34,1</t>
+          <t>-3,51; 34,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 54,13</t>
+          <t>-25,55; 60,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 64,85</t>
+          <t>-24,7; 72,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 80,85</t>
+          <t>-33,68; 81,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 991,49</t>
+          <t>-39,33; 1226,03</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 4,35</t>
+          <t>-9,95; 4,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 8,59</t>
+          <t>-3,24; 8,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 6,91</t>
+          <t>-4,57; 7,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 11,52</t>
+          <t>-21,13; 9,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 24,65</t>
+          <t>-41,27; 23,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 73,48</t>
+          <t>-18,12; 77,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 46,95</t>
+          <t>-21,86; 49,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 63,4</t>
+          <t>-66,6; 60,62</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 13,94</t>
+          <t>-3,56; 13,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 6,54</t>
+          <t>-7,83; 6,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 2,24</t>
+          <t>-13,77; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 24,51</t>
+          <t>-10,13; 23,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 97,56</t>
+          <t>-16,32; 88,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 40,5</t>
+          <t>-34,46; 38,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 10,53</t>
+          <t>-46,85; 13,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 320,15</t>
+          <t>-55,54; 319,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,39</t>
+          <t>0,54; 14,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,84</t>
+          <t>-3,13; 11,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 6,87</t>
+          <t>-6,62; 6,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 10,54</t>
+          <t>-18,99; 12,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 90,76</t>
+          <t>2,34; 88,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 60,18</t>
+          <t>-13,04; 68,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 42,1</t>
+          <t>-29,3; 43,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,22; 115,23</t>
+          <t>-74,04; 126,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,9</t>
+          <t>-0,79; 6,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,12</t>
+          <t>-1,48; 5,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,79</t>
+          <t>-3,76; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 8,7</t>
+          <t>-8,11; 9,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 37,04</t>
+          <t>-3,61; 37,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 35,59</t>
+          <t>-7,33; 34,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 15,8</t>
+          <t>-17,62; 19,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 56,66</t>
+          <t>-36,46; 62,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>11,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>116,58%</t>
+          <t>108,95%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 11,46</t>
+          <t>-7,65; 9,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 10,98</t>
+          <t>-6,3; 10,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 9,79</t>
+          <t>-6,01; 10,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 34,91</t>
+          <t>-5,51; 32,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 60,11</t>
+          <t>-27,67; 50,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 72,24</t>
+          <t>-27,71; 61,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 81,13</t>
+          <t>-31,57; 83,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 1226,03</t>
+          <t>-52,74; 853,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,83</t>
+          <t>-4,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-22,56%</t>
+          <t>-15,93%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 4,08</t>
+          <t>-8,94; 4,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,89</t>
+          <t>-3,81; 8,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 7,46</t>
+          <t>-5,02; 7,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 9,58</t>
+          <t>-21,45; 14,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 23,94</t>
+          <t>-37,28; 27,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 77,22</t>
+          <t>-22,45; 69,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 49,42</t>
+          <t>-24,13; 50,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 60,62</t>
+          <t>-66,73; 76,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 13,73</t>
+          <t>-2,07; 14,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 6,21</t>
+          <t>-8,89; 5,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 2,52</t>
+          <t>-13,54; 1,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 23,96</t>
+          <t>-9,16; 27,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 88,7</t>
+          <t>-9,32; 92,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 38,86</t>
+          <t>-35,84; 38,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 13,34</t>
+          <t>-47,5; 9,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 319,94</t>
+          <t>-54,73; 373,43</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,67</t>
+          <t>-3,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-24,48%</t>
+          <t>-20,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 14,05</t>
+          <t>0,55; 14,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 11,74</t>
+          <t>-2,91; 10,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 6,94</t>
+          <t>-6,22; 7,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 12,46</t>
+          <t>-19,88; 13,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 88,43</t>
+          <t>1,87; 91,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 68,54</t>
+          <t>-12,19; 61,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 43,17</t>
+          <t>-27,22; 43,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,04; 126,45</t>
+          <t>-75,9; 142,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,88</t>
+          <t>-0,4; 6,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,81</t>
+          <t>-1,41; 5,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,35</t>
+          <t>-4,07; 3,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,13</t>
+          <t>-7,7; 11,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 37,26</t>
+          <t>-1,47; 38,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 34,29</t>
+          <t>-6,74; 32,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 19,01</t>
+          <t>-18,97; 19,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 62,63</t>
+          <t>-32,43; 79,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>108,95%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.403690962828769</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.906269540048786</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.445905064763847</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11.01089019342452</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.06215799581073363</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0956747307153334</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.08763840948992271</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.089469370265466</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,65; 9,69</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; 10,54</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,01; 10,38</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; 32,79</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-27,67; 50,09</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-27,71; 61,89</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-31,57; 83,85</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-52,74; 853,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.645203736655914</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.302572810589672</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.010257483167925</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.507763882015437</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2766843659105595</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2771048400441601</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3156782596449259</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.527390556797305</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.687949679543644</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.54323769158002</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.37812837754951</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>32.79155526191332</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5008637217630432</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6188632971635135</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.83854268579368</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>8.532502583392331</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,87%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-15,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 4,62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 8,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,02; 7,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-21,45; 14,55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-37,28; 27,6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-22,45; 69,23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-24,13; 50,98</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-66,73; 76,97</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.475154226534412</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.622170789347458</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.043706973397732</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.28532717463003</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1186621916734444</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1758900222246049</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.05890745033555805</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1593443876287898</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-23,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62,79%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.935531423469953</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.807894249200695</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.023648537851169</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-21.45198741604899</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.372822880686169</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2245353521612597</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2412702569685876</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6672571292601469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 14,04</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,89; 5,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,54; 1,96</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,16; 27,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-9,32; 92,16</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-35,84; 38,06</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-47,5; 9,91</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-54,73; 373,43</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.624317020426673</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.364768601962675</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.181755922139532</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>14.54956244174575</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2760396313188852</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6922727840083545</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5098188215596725</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.769673488314323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,37</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,97</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,86</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-20,35%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.665107581596423</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.8611215224978513</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.795717971809888</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9.107115522865621</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2977654127437688</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.04281321538401169</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2318934041407427</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.6279424086301751</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,55; 14,12</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 10,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,22; 7,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-19,88; 13,14</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 91,06</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-12,19; 61,17</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-27,22; 43,93</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-75,9; 142,11</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.068577767514274</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.887088719751251</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.53911538790313</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.160255356581954</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.09320562193914605</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3583556573654432</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4750326782067384</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5472585716785238</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>14.03904470428977</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.831924690554563</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.961350895058223</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>27.30506317985862</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9215737600143963</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3806061348741764</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.09905009212611839</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>3.734288818299736</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.365571745305799</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.972990544860716</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2779511805497764</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.862734149543143</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3876283170129601</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1868070465608925</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01413472150566628</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2035273974427215</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.55126116075858</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.906518365154297</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.223985313855997</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-19.88338950080317</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.01874590761594416</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1218968499651988</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.272152297348721</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7590387763405849</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>14.12021697776681</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.80202065701872</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.145849000304914</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>13.14473652870968</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.910561432647662</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6117000743206652</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.439318565711598</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.421104542334291</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 6,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,41; 5,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,07; 3,25</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 11,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-1,47; 38,51</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 32,42</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-18,97; 19,2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-32,43; 79,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.067977181979411</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.179293623676071</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5151060260099621</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.056856116247168</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1512625239699349</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1152679863217762</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02633492532701259</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.05459059384139254</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.3954708645696635</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.411789704823051</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.070316105248943</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.700849886118738</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.0146858207406714</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.06741745496136373</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1897196751374538</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3242723249216224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.805964192419419</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.50101839174121</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.247968513022306</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.64560670278817</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3851342308483013</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3242313314796282</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.1920367156577792</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.7970117666297448</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
